--- a/artfynd/A 27175-2023 artfynd.xlsx
+++ b/artfynd/A 27175-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457073</v>
       </c>
       <c r="B2" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27175-2023 artfynd.xlsx
+++ b/artfynd/A 27175-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457073</v>
       </c>
       <c r="B2" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27175-2023 artfynd.xlsx
+++ b/artfynd/A 27175-2023 artfynd.xlsx
@@ -709,11 +709,7 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lyckoträsk, Nb</t>

--- a/artfynd/A 27175-2023 artfynd.xlsx
+++ b/artfynd/A 27175-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457073</v>
       </c>
       <c r="B2" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27175-2023 artfynd.xlsx
+++ b/artfynd/A 27175-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457073</v>
       </c>
       <c r="B2" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27175-2023 artfynd.xlsx
+++ b/artfynd/A 27175-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457073</v>
       </c>
       <c r="B2" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
